--- a/outputs/monitor_xlsx/20260223.xlsx
+++ b/outputs/monitor_xlsx/20260223.xlsx
@@ -999,7 +999,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V27"/>
+  <dimension ref="A1:V28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -2365,13 +2365,13 @@
         <v>1189</v>
       </c>
       <c r="L26" t="n">
-        <v>4686</v>
+        <v>3788</v>
       </c>
       <c r="M26" t="n">
         <v>-106281</v>
       </c>
       <c r="N26" t="n">
-        <v>12.8</v>
+        <v>11.49</v>
       </c>
       <c r="O26" t="inlineStr">
         <is>
@@ -2429,6 +2429,59 @@
       <c r="O27" t="inlineStr">
         <is>
           <t>中性</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>6515</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>穎崴</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>4695</v>
+      </c>
+      <c r="D28" s="7" t="n">
+        <v>-6.19</v>
+      </c>
+      <c r="E28" t="n">
+        <v>781</v>
+      </c>
+      <c r="F28" s="6" t="n">
+        <v>-111</v>
+      </c>
+      <c r="G28" t="n">
+        <v>-197</v>
+      </c>
+      <c r="H28" t="n">
+        <v>-89</v>
+      </c>
+      <c r="I28" t="n">
+        <v>-42</v>
+      </c>
+      <c r="J28" t="n">
+        <v>40</v>
+      </c>
+      <c r="K28" t="n">
+        <v>382</v>
+      </c>
+      <c r="L28" t="n">
+        <v>1697</v>
+      </c>
+      <c r="M28" t="n">
+        <v>-8886</v>
+      </c>
+      <c r="N28" t="n">
+        <v>-0.28</v>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>主力積極賣出</t>
         </is>
       </c>
     </row>

--- a/outputs/monitor_xlsx/20260223.xlsx
+++ b/outputs/monitor_xlsx/20260223.xlsx
@@ -481,6 +481,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -823,6 +824,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
@@ -878,6 +880,7 @@
         </is>
       </c>
     </row>
+    <row r="8"/>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
@@ -999,7 +1002,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V28"/>
+  <dimension ref="A1:U28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1107,40 +1110,35 @@
       </c>
       <c r="O3" s="5" t="inlineStr">
         <is>
-          <t>籌碼評價</t>
+          <t>買賣券商差</t>
         </is>
       </c>
       <c r="P3" s="5" t="inlineStr">
         <is>
-          <t>買賣券商差</t>
+          <t>籌碼集中度5D(%)</t>
         </is>
       </c>
       <c r="Q3" s="5" t="inlineStr">
         <is>
-          <t>籌碼集中度5D(%)</t>
+          <t>借券賣出餘額</t>
         </is>
       </c>
       <c r="R3" s="5" t="inlineStr">
         <is>
-          <t>借券賣出餘額</t>
+          <t>短回補天數</t>
         </is>
       </c>
       <c r="S3" s="5" t="inlineStr">
         <is>
-          <t>短回補天數</t>
+          <t>VWAP20D</t>
         </is>
       </c>
       <c r="T3" s="5" t="inlineStr">
         <is>
-          <t>VWAP20D</t>
+          <t>VWAP乖離(%)</t>
         </is>
       </c>
       <c r="U3" s="5" t="inlineStr">
-        <is>
-          <t>VWAP乖離(%)</t>
-        </is>
-      </c>
-      <c r="V3" s="5" t="inlineStr">
         <is>
           <t>資料來源</t>
         </is>
@@ -1190,12 +1188,7 @@
       <c r="M4" t="n">
         <v>-4053858</v>
       </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>中性</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1233,12 +1226,7 @@
       <c r="M5" t="n">
         <v>-28396</v>
       </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>中性</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1288,12 +1276,7 @@
       <c r="M6" t="n">
         <v>-78754</v>
       </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>中性</t>
-        </is>
-      </c>
-      <c r="V6" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1340,12 +1323,7 @@
       <c r="M7" t="n">
         <v>-1105588</v>
       </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>中性</t>
-        </is>
-      </c>
-      <c r="V7" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1395,12 +1373,7 @@
       <c r="M8" t="n">
         <v>-648667</v>
       </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>中性</t>
-        </is>
-      </c>
-      <c r="V8" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1450,12 +1423,7 @@
       <c r="M9" t="n">
         <v>-6482905</v>
       </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>中性</t>
-        </is>
-      </c>
-      <c r="V9" t="inlineStr">
+      <c r="U9" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1505,12 +1473,7 @@
       <c r="M10" t="n">
         <v>-1110979</v>
       </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>中性</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
+      <c r="U10" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1560,12 +1523,7 @@
       <c r="M11" t="n">
         <v>-89484</v>
       </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>中性</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr">
+      <c r="U11" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1615,12 +1573,7 @@
       <c r="M12" t="n">
         <v>-19728</v>
       </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>中性</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
+      <c r="U12" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1670,12 +1623,7 @@
       <c r="M13" t="n">
         <v>-267398</v>
       </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>中性</t>
-        </is>
-      </c>
-      <c r="V13" t="inlineStr">
+      <c r="U13" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1725,12 +1673,7 @@
       <c r="M14" t="n">
         <v>-19172</v>
       </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>中性</t>
-        </is>
-      </c>
-      <c r="V14" t="inlineStr">
+      <c r="U14" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1780,12 +1723,7 @@
       <c r="M15" t="n">
         <v>0</v>
       </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>中性</t>
-        </is>
-      </c>
-      <c r="V15" t="inlineStr">
+      <c r="U15" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1835,12 +1773,7 @@
       <c r="M16" t="n">
         <v>0</v>
       </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>中性</t>
-        </is>
-      </c>
-      <c r="V16" t="inlineStr">
+      <c r="U16" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1887,12 +1820,7 @@
       <c r="M17" t="n">
         <v>0</v>
       </c>
-      <c r="O17" t="inlineStr">
-        <is>
-          <t>中性</t>
-        </is>
-      </c>
-      <c r="V17" t="inlineStr">
+      <c r="U17" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1942,12 +1870,7 @@
       <c r="M18" t="n">
         <v>0</v>
       </c>
-      <c r="O18" t="inlineStr">
-        <is>
-          <t>中性</t>
-        </is>
-      </c>
-      <c r="V18" t="inlineStr">
+      <c r="U18" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1997,12 +1920,7 @@
       <c r="M19" t="n">
         <v>-113430</v>
       </c>
-      <c r="O19" t="inlineStr">
-        <is>
-          <t>中性</t>
-        </is>
-      </c>
-      <c r="V19" t="inlineStr">
+      <c r="U19" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -2055,11 +1973,6 @@
       <c r="N20" t="n">
         <v>4.43</v>
       </c>
-      <c r="O20" t="inlineStr">
-        <is>
-          <t>中性</t>
-        </is>
-      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2108,11 +2021,6 @@
       <c r="N21" t="n">
         <v>-2.27</v>
       </c>
-      <c r="O21" t="inlineStr">
-        <is>
-          <t>主力積極賣出</t>
-        </is>
-      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2161,11 +2069,6 @@
       <c r="N22" t="n">
         <v>0.18</v>
       </c>
-      <c r="O22" t="inlineStr">
-        <is>
-          <t>中性</t>
-        </is>
-      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2214,11 +2117,6 @@
       <c r="N23" t="n">
         <v>15.77</v>
       </c>
-      <c r="O23" t="inlineStr">
-        <is>
-          <t>偏多</t>
-        </is>
-      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2267,11 +2165,6 @@
       <c r="N24" t="n">
         <v>0</v>
       </c>
-      <c r="O24" t="inlineStr">
-        <is>
-          <t>偏多</t>
-        </is>
-      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2320,11 +2213,6 @@
       <c r="N25" t="n">
         <v>0</v>
       </c>
-      <c r="O25" t="inlineStr">
-        <is>
-          <t>主力積極買進</t>
-        </is>
-      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2373,11 +2261,6 @@
       <c r="N26" t="n">
         <v>11.49</v>
       </c>
-      <c r="O26" t="inlineStr">
-        <is>
-          <t>中性</t>
-        </is>
-      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -2426,11 +2309,6 @@
       <c r="N27" t="n">
         <v>11.96</v>
       </c>
-      <c r="O27" t="inlineStr">
-        <is>
-          <t>中性</t>
-        </is>
-      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -2478,11 +2356,6 @@
       </c>
       <c r="N28" t="n">
         <v>-0.28</v>
-      </c>
-      <c r="O28" t="inlineStr">
-        <is>
-          <t>主力積極賣出</t>
-        </is>
       </c>
     </row>
   </sheetData>

--- a/outputs/monitor_xlsx/20260223.xlsx
+++ b/outputs/monitor_xlsx/20260223.xlsx
@@ -481,7 +481,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -824,7 +823,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
@@ -880,7 +878,6 @@
         </is>
       </c>
     </row>
-    <row r="8"/>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
@@ -1002,7 +999,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U28"/>
+  <dimension ref="A1:U29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -2358,6 +2355,51 @@
         <v>-0.28</v>
       </c>
     </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>3167</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>大量</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>278</v>
+      </c>
+      <c r="D29" s="6" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="E29" t="n">
+        <v>10762</v>
+      </c>
+      <c r="F29" s="6" t="n">
+        <v>-1118</v>
+      </c>
+      <c r="G29" t="n">
+        <v>6862</v>
+      </c>
+      <c r="H29" t="n">
+        <v>268</v>
+      </c>
+      <c r="I29" t="n">
+        <v>743</v>
+      </c>
+      <c r="J29" t="n">
+        <v>61</v>
+      </c>
+      <c r="K29" t="n">
+        <v>6618</v>
+      </c>
+      <c r="L29" t="n">
+        <v>18469</v>
+      </c>
+      <c r="M29" t="n">
+        <v>-21226</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:O1"/>

--- a/outputs/monitor_xlsx/20260223.xlsx
+++ b/outputs/monitor_xlsx/20260223.xlsx
@@ -1149,41 +1149,49 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0050</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
+          <t>元大台灣50</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="n">
         <v>77.40000000000001</v>
       </c>
-      <c r="D4" s="6" t="n">
+      <c r="E4" s="6" t="n">
         <v>0.26</v>
       </c>
-      <c r="E4" t="n">
+      <c r="F4" s="6" t="n">
         <v>227936</v>
       </c>
-      <c r="F4" s="6" t="n">
+      <c r="G4" s="6" t="n">
         <v>-61521</v>
       </c>
-      <c r="G4" t="n">
-        <v>0</v>
-      </c>
       <c r="H4" t="n">
+        <v>-27120</v>
+      </c>
+      <c r="I4" t="n">
         <v>7700</v>
       </c>
-      <c r="I4" t="n">
-        <v>0</v>
-      </c>
       <c r="J4" t="n">
+        <v>25026</v>
+      </c>
+      <c r="K4" t="n">
         <v>93953</v>
       </c>
-      <c r="K4" t="n">
+      <c r="L4" t="n">
         <v>7621</v>
       </c>
-      <c r="L4" t="n">
-        <v>0</v>
-      </c>
       <c r="M4" t="n">
+        <v>37320</v>
+      </c>
+      <c r="N4" t="n">
         <v>-4053858</v>
+      </c>
+      <c r="O4" t="n">
+        <v>5.72</v>
       </c>
       <c r="U4" t="inlineStr">
         <is>
@@ -1240,38 +1248,46 @@
           <t>華城</t>
         </is>
       </c>
-      <c r="C6" t="n">
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="n">
         <v>966</v>
       </c>
-      <c r="D6" s="7" t="n">
+      <c r="E6" s="7" t="n">
         <v>-0.1</v>
       </c>
-      <c r="E6" t="n">
+      <c r="F6" s="7" t="n">
         <v>4215</v>
       </c>
-      <c r="F6" s="7" t="n">
+      <c r="G6" s="7" t="n">
         <v>144</v>
       </c>
-      <c r="G6" t="n">
-        <v>0</v>
-      </c>
       <c r="H6" t="n">
+        <v>1730</v>
+      </c>
+      <c r="I6" t="n">
         <v>-589</v>
       </c>
-      <c r="I6" t="n">
-        <v>0</v>
-      </c>
       <c r="J6" t="n">
+        <v>-1154</v>
+      </c>
+      <c r="K6" t="n">
         <v>111</v>
       </c>
-      <c r="K6" t="n">
+      <c r="L6" t="n">
         <v>2872</v>
       </c>
-      <c r="L6" t="n">
-        <v>0</v>
-      </c>
       <c r="M6" t="n">
+        <v>14357</v>
+      </c>
+      <c r="N6" t="n">
         <v>-78754</v>
+      </c>
+      <c r="O6" t="n">
+        <v>-2.01</v>
       </c>
       <c r="U6" t="inlineStr">
         <is>
@@ -1337,38 +1353,46 @@
           <t>台達電</t>
         </is>
       </c>
-      <c r="C8" t="n">
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="n">
         <v>1305</v>
       </c>
-      <c r="D8" s="6" t="n">
+      <c r="E8" s="6" t="n">
         <v>3.57</v>
       </c>
-      <c r="E8" t="n">
+      <c r="F8" s="7" t="n">
         <v>22078</v>
       </c>
-      <c r="F8" s="7" t="n">
+      <c r="G8" s="7" t="n">
         <v>1710</v>
       </c>
-      <c r="G8" t="n">
-        <v>0</v>
-      </c>
       <c r="H8" t="n">
+        <v>1292</v>
+      </c>
+      <c r="I8" t="n">
         <v>766</v>
       </c>
-      <c r="I8" t="n">
-        <v>0</v>
-      </c>
       <c r="J8" t="n">
+        <v>1974</v>
+      </c>
+      <c r="K8" t="n">
         <v>832</v>
       </c>
-      <c r="K8" t="n">
+      <c r="L8" t="n">
         <v>6544</v>
       </c>
-      <c r="L8" t="n">
-        <v>0</v>
-      </c>
       <c r="M8" t="n">
+        <v>31255</v>
+      </c>
+      <c r="N8" t="n">
         <v>-648667</v>
+      </c>
+      <c r="O8" t="n">
+        <v>8.34</v>
       </c>
       <c r="U8" t="inlineStr">
         <is>
@@ -1387,38 +1411,46 @@
           <t>台積電</t>
         </is>
       </c>
-      <c r="C9" t="n">
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="D9" s="7" t="n">
         <v>1900</v>
       </c>
-      <c r="D9" s="7" t="n">
+      <c r="E9" s="7" t="n">
         <v>-0.78</v>
       </c>
-      <c r="E9" t="n">
+      <c r="F9" s="6" t="n">
         <v>80768</v>
       </c>
-      <c r="F9" s="6" t="n">
+      <c r="G9" s="6" t="n">
         <v>-17559</v>
       </c>
-      <c r="G9" t="n">
-        <v>0</v>
-      </c>
       <c r="H9" t="n">
+        <v>-13521</v>
+      </c>
+      <c r="I9" t="n">
         <v>2322</v>
       </c>
-      <c r="I9" t="n">
-        <v>0</v>
-      </c>
       <c r="J9" t="n">
+        <v>4933</v>
+      </c>
+      <c r="K9" t="n">
         <v>2063</v>
       </c>
-      <c r="K9" t="n">
+      <c r="L9" t="n">
         <v>21832</v>
       </c>
-      <c r="L9" t="n">
-        <v>0</v>
-      </c>
       <c r="M9" t="n">
+        <v>110248</v>
+      </c>
+      <c r="N9" t="n">
         <v>-6482905</v>
+      </c>
+      <c r="O9" t="n">
+        <v>5.89</v>
       </c>
       <c r="U9" t="inlineStr">
         <is>
@@ -1487,38 +1519,46 @@
           <t>台光電</t>
         </is>
       </c>
-      <c r="C11" t="n">
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="D11" s="7" t="n">
         <v>2175</v>
       </c>
-      <c r="D11" s="7" t="n">
+      <c r="E11" s="7" t="n">
         <v>-0.91</v>
       </c>
-      <c r="E11" t="n">
+      <c r="F11" s="6" t="n">
         <v>4407</v>
       </c>
-      <c r="F11" s="6" t="n">
+      <c r="G11" s="6" t="n">
         <v>-245</v>
       </c>
-      <c r="G11" t="n">
-        <v>0</v>
-      </c>
       <c r="H11" t="n">
+        <v>-2134</v>
+      </c>
+      <c r="I11" t="n">
         <v>26</v>
       </c>
-      <c r="I11" t="n">
-        <v>0</v>
-      </c>
       <c r="J11" t="n">
+        <v>1919</v>
+      </c>
+      <c r="K11" t="n">
         <v>315</v>
       </c>
-      <c r="K11" t="n">
+      <c r="L11" t="n">
         <v>2223</v>
       </c>
-      <c r="L11" t="n">
-        <v>0</v>
-      </c>
       <c r="M11" t="n">
+        <v>10853</v>
+      </c>
+      <c r="N11" t="n">
         <v>-89484</v>
+      </c>
+      <c r="O11" t="n">
+        <v>17.74</v>
       </c>
       <c r="U11" t="inlineStr">
         <is>
@@ -1637,38 +1677,46 @@
           <t>光聖</t>
         </is>
       </c>
-      <c r="C14" t="n">
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="D14" s="6" t="n">
         <v>2035</v>
       </c>
-      <c r="D14" s="6" t="n">
+      <c r="E14" s="6" t="n">
         <v>4.36</v>
       </c>
-      <c r="E14" t="n">
+      <c r="F14" s="7" t="n">
         <v>984</v>
       </c>
-      <c r="F14" s="7" t="n">
+      <c r="G14" s="7" t="n">
         <v>27</v>
       </c>
-      <c r="G14" t="n">
-        <v>0</v>
-      </c>
       <c r="H14" t="n">
+        <v>543</v>
+      </c>
+      <c r="I14" t="n">
         <v>19</v>
       </c>
-      <c r="I14" t="n">
-        <v>0</v>
-      </c>
       <c r="J14" t="n">
+        <v>7</v>
+      </c>
+      <c r="K14" t="n">
         <v>17</v>
       </c>
-      <c r="K14" t="n">
+      <c r="L14" t="n">
         <v>4215</v>
       </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
       <c r="M14" t="n">
+        <v>21194</v>
+      </c>
+      <c r="N14" t="n">
         <v>-19172</v>
+      </c>
+      <c r="O14" t="n">
+        <v>26.63</v>
       </c>
       <c r="U14" t="inlineStr">
         <is>
@@ -1687,37 +1735,45 @@
           <t>聯亞</t>
         </is>
       </c>
-      <c r="C15" t="n">
-        <v>1190</v>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
       </c>
       <c r="D15" s="6" t="n">
-        <v>9.68</v>
-      </c>
-      <c r="E15" t="n">
-        <v>812</v>
+        <v>2365</v>
+      </c>
+      <c r="E15" s="6" t="n">
+        <v>2.16</v>
       </c>
       <c r="F15" s="6" t="n">
+        <v>2182</v>
+      </c>
+      <c r="G15" s="6" t="n">
         <v>-173</v>
       </c>
-      <c r="G15" t="n">
-        <v>0</v>
-      </c>
       <c r="H15" t="n">
+        <v>44</v>
+      </c>
+      <c r="I15" t="n">
         <v>113</v>
       </c>
-      <c r="I15" t="n">
-        <v>0</v>
-      </c>
       <c r="J15" t="n">
+        <v>151</v>
+      </c>
+      <c r="K15" t="n">
         <v>88</v>
       </c>
-      <c r="K15" t="n">
+      <c r="L15" t="n">
         <v>-22</v>
       </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
       <c r="M15" t="n">
+        <v>-227</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
         <v>0</v>
       </c>
       <c r="U15" t="inlineStr">
@@ -1834,37 +1890,45 @@
           <t>華星光</t>
         </is>
       </c>
-      <c r="C18" t="n">
-        <v>357.5</v>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
       </c>
       <c r="D18" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="E18" t="n">
-        <v>25333</v>
+        <v>586</v>
+      </c>
+      <c r="E18" s="6" t="n">
+        <v>9.94</v>
       </c>
       <c r="F18" s="7" t="n">
+        <v>32773</v>
+      </c>
+      <c r="G18" s="7" t="n">
         <v>3379</v>
       </c>
-      <c r="G18" t="n">
-        <v>0</v>
-      </c>
       <c r="H18" t="n">
+        <v>1308</v>
+      </c>
+      <c r="I18" t="n">
         <v>1747</v>
       </c>
-      <c r="I18" t="n">
-        <v>0</v>
-      </c>
       <c r="J18" t="n">
+        <v>2540</v>
+      </c>
+      <c r="K18" t="n">
         <v>231</v>
       </c>
-      <c r="K18" t="n">
+      <c r="L18" t="n">
         <v>-404</v>
       </c>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
       <c r="M18" t="n">
+        <v>-645</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" t="n">
         <v>0</v>
       </c>
       <c r="U18" t="inlineStr">
@@ -2078,40 +2142,45 @@
           <t>智邦</t>
         </is>
       </c>
-      <c r="C23" t="n">
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="D23" s="7" t="n">
         <v>1400</v>
       </c>
-      <c r="D23" s="7" t="n">
+      <c r="E23" s="7" t="n">
         <v>-3.45</v>
       </c>
-      <c r="E23" t="n">
+      <c r="F23" s="6" t="n">
         <v>7796</v>
       </c>
-      <c r="F23" s="6" t="n">
+      <c r="G23" s="6" t="n">
         <v>-154</v>
       </c>
-      <c r="G23" t="n">
+      <c r="H23" t="n">
         <v>4385</v>
       </c>
-      <c r="H23" t="n">
+      <c r="I23" t="n">
         <v>106</v>
       </c>
-      <c r="I23" t="n">
+      <c r="J23" t="n">
         <v>2036</v>
       </c>
-      <c r="J23" t="n">
+      <c r="K23" t="n">
         <v>334</v>
       </c>
-      <c r="K23" t="n">
+      <c r="L23" t="n">
         <v>1817</v>
       </c>
-      <c r="L23" t="n">
+      <c r="M23" t="n">
         <v>11033</v>
       </c>
-      <c r="M23" t="n">
+      <c r="N23" t="n">
         <v>-140143</v>
       </c>
-      <c r="N23" t="n">
+      <c r="O23" t="n">
         <v>15.77</v>
       </c>
     </row>
@@ -2126,40 +2195,45 @@
           <t>均華</t>
         </is>
       </c>
-      <c r="C24" t="n">
-        <v>962</v>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
       </c>
       <c r="D24" s="7" t="n">
-        <v>-0.1</v>
-      </c>
-      <c r="E24" t="n">
-        <v>826</v>
+        <v>1625</v>
+      </c>
+      <c r="E24" s="7" t="n">
+        <v>-6.07</v>
       </c>
       <c r="F24" s="7" t="n">
+        <v>1168</v>
+      </c>
+      <c r="G24" s="7" t="n">
         <v>25</v>
       </c>
-      <c r="G24" t="n">
+      <c r="H24" t="n">
         <v>55</v>
       </c>
-      <c r="H24" t="n">
+      <c r="I24" t="n">
         <v>-67</v>
       </c>
-      <c r="I24" t="n">
+      <c r="J24" t="n">
         <v>-83</v>
       </c>
-      <c r="J24" t="n">
+      <c r="K24" t="n">
         <v>-1</v>
       </c>
-      <c r="K24" t="n">
+      <c r="L24" t="n">
         <v>13</v>
       </c>
-      <c r="L24" t="n">
+      <c r="M24" t="n">
         <v>-46</v>
       </c>
-      <c r="M24" t="n">
-        <v>0</v>
-      </c>
       <c r="N24" t="n">
+        <v>0</v>
+      </c>
+      <c r="O24" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2174,40 +2248,45 @@
           <t>萬潤</t>
         </is>
       </c>
-      <c r="C25" t="n">
-        <v>624</v>
-      </c>
-      <c r="D25" s="6" t="n">
-        <v>6.48</v>
-      </c>
-      <c r="E25" t="n">
-        <v>2040</v>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="D25" s="7" t="n">
+        <v>1105</v>
+      </c>
+      <c r="E25" s="7" t="n">
+        <v>-2.64</v>
       </c>
       <c r="F25" s="7" t="n">
+        <v>6341</v>
+      </c>
+      <c r="G25" s="7" t="n">
         <v>3732</v>
       </c>
-      <c r="G25" t="n">
+      <c r="H25" t="n">
         <v>5773</v>
       </c>
-      <c r="H25" t="n">
-        <v>0</v>
-      </c>
       <c r="I25" t="n">
         <v>0</v>
       </c>
       <c r="J25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" t="n">
         <v>248</v>
       </c>
-      <c r="K25" t="n">
+      <c r="L25" t="n">
         <v>-210</v>
       </c>
-      <c r="L25" t="n">
+      <c r="M25" t="n">
         <v>-411</v>
       </c>
-      <c r="M25" t="n">
-        <v>0</v>
-      </c>
       <c r="N25" t="n">
+        <v>0</v>
+      </c>
+      <c r="O25" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2222,41 +2301,46 @@
           <t>致茂</t>
         </is>
       </c>
-      <c r="C26" t="n">
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="D26" s="6" t="n">
         <v>1155</v>
       </c>
-      <c r="D26" s="6" t="n">
+      <c r="E26" s="6" t="n">
         <v>10</v>
       </c>
-      <c r="E26" t="n">
+      <c r="F26" s="6" t="n">
         <v>3903</v>
       </c>
-      <c r="F26" s="6" t="n">
+      <c r="G26" s="6" t="n">
         <v>-350</v>
       </c>
-      <c r="G26" t="n">
+      <c r="H26" t="n">
         <v>683</v>
       </c>
-      <c r="H26" t="n">
+      <c r="I26" t="n">
         <v>50</v>
       </c>
-      <c r="I26" t="n">
+      <c r="J26" t="n">
         <v>-172</v>
       </c>
-      <c r="J26" t="n">
+      <c r="K26" t="n">
         <v>160</v>
       </c>
-      <c r="K26" t="n">
+      <c r="L26" t="n">
         <v>1189</v>
       </c>
-      <c r="L26" t="n">
-        <v>3788</v>
-      </c>
       <c r="M26" t="n">
+        <v>4686</v>
+      </c>
+      <c r="N26" t="n">
         <v>-106281</v>
       </c>
-      <c r="N26" t="n">
-        <v>11.49</v>
+      <c r="O26" t="n">
+        <v>13.59</v>
       </c>
     </row>
     <row r="27">
@@ -2318,41 +2402,46 @@
           <t>穎崴</t>
         </is>
       </c>
-      <c r="C28" t="n">
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="D28" s="7" t="n">
         <v>4695</v>
       </c>
-      <c r="D28" s="7" t="n">
+      <c r="E28" s="7" t="n">
         <v>-6.19</v>
       </c>
-      <c r="E28" t="n">
+      <c r="F28" s="6" t="n">
         <v>781</v>
       </c>
-      <c r="F28" s="6" t="n">
+      <c r="G28" s="6" t="n">
         <v>-111</v>
       </c>
-      <c r="G28" t="n">
+      <c r="H28" t="n">
         <v>-197</v>
       </c>
-      <c r="H28" t="n">
+      <c r="I28" t="n">
         <v>-89</v>
       </c>
-      <c r="I28" t="n">
+      <c r="J28" t="n">
         <v>-42</v>
       </c>
-      <c r="J28" t="n">
+      <c r="K28" t="n">
         <v>40</v>
       </c>
-      <c r="K28" t="n">
+      <c r="L28" t="n">
         <v>382</v>
       </c>
-      <c r="L28" t="n">
+      <c r="M28" t="n">
         <v>1697</v>
       </c>
-      <c r="M28" t="n">
+      <c r="N28" t="n">
         <v>-8886</v>
       </c>
-      <c r="N28" t="n">
-        <v>-0.28</v>
+      <c r="O28" t="n">
+        <v>12.18</v>
       </c>
     </row>
     <row r="29">
@@ -2366,38 +2455,46 @@
           <t>大量</t>
         </is>
       </c>
-      <c r="C29" t="n">
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="D29" s="6" t="n">
         <v>278</v>
       </c>
-      <c r="D29" s="6" t="n">
+      <c r="E29" s="6" t="n">
         <v>2.39</v>
       </c>
-      <c r="E29" t="n">
+      <c r="F29" s="6" t="n">
         <v>10762</v>
       </c>
-      <c r="F29" s="6" t="n">
+      <c r="G29" s="6" t="n">
         <v>-1118</v>
       </c>
-      <c r="G29" t="n">
-        <v>6862</v>
-      </c>
       <c r="H29" t="n">
+        <v>11228</v>
+      </c>
+      <c r="I29" t="n">
         <v>268</v>
       </c>
-      <c r="I29" t="n">
-        <v>743</v>
-      </c>
       <c r="J29" t="n">
+        <v>856</v>
+      </c>
+      <c r="K29" t="n">
         <v>61</v>
       </c>
-      <c r="K29" t="n">
+      <c r="L29" t="n">
         <v>6618</v>
       </c>
-      <c r="L29" t="n">
-        <v>18469</v>
-      </c>
       <c r="M29" t="n">
+        <v>30918</v>
+      </c>
+      <c r="N29" t="n">
         <v>-21226</v>
+      </c>
+      <c r="O29" t="n">
+        <v>20.27</v>
       </c>
     </row>
   </sheetData>
